--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121274056</v>
+        <v>121273772</v>
       </c>
       <c r="B2" t="n">
-        <v>5169</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692000</v>
+        <v>691997</v>
       </c>
       <c r="R2" t="n">
-        <v>7128433</v>
+        <v>7128437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -794,7 +794,7 @@
         <v>121273867</v>
       </c>
       <c r="B3" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121273967</v>
+        <v>121274009</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>82385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691964</v>
+        <v>691994</v>
       </c>
       <c r="R4" t="n">
-        <v>7128470</v>
+        <v>7128443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121273772</v>
+        <v>121274056</v>
       </c>
       <c r="B5" t="n">
-        <v>90687</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691997</v>
+        <v>692000</v>
       </c>
       <c r="R5" t="n">
-        <v>7128437</v>
+        <v>7128433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121274009</v>
+        <v>121273967</v>
       </c>
       <c r="B6" t="n">
-        <v>82382</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691994</v>
+        <v>691964</v>
       </c>
       <c r="R6" t="n">
-        <v>7128443</v>
+        <v>7128470</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121273867</v>
+        <v>121274009</v>
       </c>
       <c r="B3" t="n">
-        <v>56566</v>
+        <v>82385</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691978</v>
+        <v>691994</v>
       </c>
       <c r="R3" t="n">
-        <v>7128474</v>
+        <v>7128443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121274009</v>
+        <v>121273867</v>
       </c>
       <c r="B4" t="n">
-        <v>82385</v>
+        <v>56566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691994</v>
+        <v>691978</v>
       </c>
       <c r="R4" t="n">
-        <v>7128443</v>
+        <v>7128474</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121274009</v>
+        <v>121273867</v>
       </c>
       <c r="B3" t="n">
-        <v>82385</v>
+        <v>56566</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691994</v>
+        <v>691978</v>
       </c>
       <c r="R3" t="n">
-        <v>7128443</v>
+        <v>7128474</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121273867</v>
+        <v>121274009</v>
       </c>
       <c r="B4" t="n">
-        <v>56566</v>
+        <v>82385</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691978</v>
+        <v>691994</v>
       </c>
       <c r="R4" t="n">
-        <v>7128474</v>
+        <v>7128443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121273772</v>
+        <v>121273867</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
+        <v>56566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691997</v>
+        <v>691978</v>
       </c>
       <c r="R2" t="n">
-        <v>7128437</v>
+        <v>7128474</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121273867</v>
+        <v>121273967</v>
       </c>
       <c r="B3" t="n">
-        <v>56566</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691978</v>
+        <v>691964</v>
       </c>
       <c r="R3" t="n">
-        <v>7128474</v>
+        <v>7128470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121274009</v>
+        <v>121274056</v>
       </c>
       <c r="B4" t="n">
-        <v>82385</v>
+        <v>5169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691994</v>
+        <v>692000</v>
       </c>
       <c r="R4" t="n">
-        <v>7128443</v>
+        <v>7128433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121274056</v>
+        <v>121274009</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>82385</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692000</v>
+        <v>691994</v>
       </c>
       <c r="R5" t="n">
-        <v>7128433</v>
+        <v>7128443</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121273967</v>
+        <v>121273772</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691964</v>
+        <v>691997</v>
       </c>
       <c r="R6" t="n">
-        <v>7128470</v>
+        <v>7128437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121273967</v>
+        <v>121274009</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691964</v>
+        <v>691994</v>
       </c>
       <c r="R3" t="n">
-        <v>7128470</v>
+        <v>7128443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121274056</v>
+        <v>121273772</v>
       </c>
       <c r="B4" t="n">
-        <v>5169</v>
+        <v>90709</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692000</v>
+        <v>691997</v>
       </c>
       <c r="R4" t="n">
-        <v>7128433</v>
+        <v>7128437</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121274009</v>
+        <v>121273967</v>
       </c>
       <c r="B5" t="n">
-        <v>82385</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,21 +1039,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691994</v>
+        <v>691964</v>
       </c>
       <c r="R5" t="n">
-        <v>7128443</v>
+        <v>7128470</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121273772</v>
+        <v>121274056</v>
       </c>
       <c r="B6" t="n">
-        <v>90697</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1151,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691997</v>
+        <v>692000</v>
       </c>
       <c r="R6" t="n">
-        <v>7128437</v>
+        <v>7128433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121273867</v>
+        <v>121273772</v>
       </c>
       <c r="B2" t="n">
-        <v>56566</v>
+        <v>90710</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691978</v>
+        <v>691997</v>
       </c>
       <c r="R2" t="n">
-        <v>7128474</v>
+        <v>7128437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121274009</v>
+        <v>121273967</v>
       </c>
       <c r="B3" t="n">
-        <v>82388</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691994</v>
+        <v>691964</v>
       </c>
       <c r="R3" t="n">
-        <v>7128443</v>
+        <v>7128470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121273772</v>
+        <v>121273867</v>
       </c>
       <c r="B4" t="n">
-        <v>90709</v>
+        <v>56566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691997</v>
+        <v>691978</v>
       </c>
       <c r="R4" t="n">
-        <v>7128437</v>
+        <v>7128474</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121273967</v>
+        <v>121274056</v>
       </c>
       <c r="B5" t="n">
-        <v>78604</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691964</v>
+        <v>692000</v>
       </c>
       <c r="R5" t="n">
-        <v>7128470</v>
+        <v>7128433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121274056</v>
+        <v>121274009</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>82388</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1151,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692000</v>
+        <v>691994</v>
       </c>
       <c r="R6" t="n">
-        <v>7128433</v>
+        <v>7128443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121273772</v>
+        <v>121274056</v>
       </c>
       <c r="B2" t="n">
-        <v>90710</v>
+        <v>5172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691997</v>
+        <v>692000</v>
       </c>
       <c r="R2" t="n">
-        <v>7128437</v>
+        <v>7128433</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121273967</v>
+        <v>121273772</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691964</v>
+        <v>691997</v>
       </c>
       <c r="R3" t="n">
-        <v>7128470</v>
+        <v>7128437</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,7 +910,7 @@
         <v>121273867</v>
       </c>
       <c r="B4" t="n">
-        <v>56566</v>
+        <v>56569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121274056</v>
+        <v>121273967</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692000</v>
+        <v>691964</v>
       </c>
       <c r="R5" t="n">
-        <v>7128433</v>
+        <v>7128470</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1142,7 +1142,7 @@
         <v>121274009</v>
       </c>
       <c r="B6" t="n">
-        <v>82388</v>
+        <v>82391</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121274056</v>
+        <v>121273772</v>
       </c>
       <c r="B2" t="n">
-        <v>5172</v>
+        <v>90713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692000</v>
+        <v>691997</v>
       </c>
       <c r="R2" t="n">
-        <v>7128433</v>
+        <v>7128437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121273772</v>
+        <v>121274009</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>82391</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691997</v>
+        <v>691994</v>
       </c>
       <c r="R3" t="n">
-        <v>7128437</v>
+        <v>7128443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121273867</v>
+        <v>121274056</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>5172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691978</v>
+        <v>692000</v>
       </c>
       <c r="R4" t="n">
-        <v>7128474</v>
+        <v>7128433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121273967</v>
+        <v>121273867</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>56569</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691964</v>
+        <v>691978</v>
       </c>
       <c r="R5" t="n">
-        <v>7128470</v>
+        <v>7128474</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121274009</v>
+        <v>121273967</v>
       </c>
       <c r="B6" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691994</v>
+        <v>691964</v>
       </c>
       <c r="R6" t="n">
-        <v>7128443</v>
+        <v>7128470</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121274009</v>
+        <v>121274056</v>
       </c>
       <c r="B3" t="n">
-        <v>82391</v>
+        <v>5172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691994</v>
+        <v>692000</v>
       </c>
       <c r="R3" t="n">
-        <v>7128443</v>
+        <v>7128433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121274056</v>
+        <v>121274009</v>
       </c>
       <c r="B4" t="n">
-        <v>5172</v>
+        <v>82391</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692000</v>
+        <v>691994</v>
       </c>
       <c r="R4" t="n">
-        <v>7128433</v>
+        <v>7128443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121273772</v>
+        <v>121274009</v>
       </c>
       <c r="B2" t="n">
-        <v>90713</v>
+        <v>82392</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691997</v>
+        <v>691994</v>
       </c>
       <c r="R2" t="n">
-        <v>7128437</v>
+        <v>7128443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121274009</v>
+        <v>121273772</v>
       </c>
       <c r="B4" t="n">
-        <v>82391</v>
+        <v>90719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691994</v>
+        <v>691997</v>
       </c>
       <c r="R4" t="n">
-        <v>7128443</v>
+        <v>7128437</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121273867</v>
+        <v>121273967</v>
       </c>
       <c r="B5" t="n">
-        <v>56569</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691978</v>
+        <v>691964</v>
       </c>
       <c r="R5" t="n">
-        <v>7128474</v>
+        <v>7128470</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121273967</v>
+        <v>121273867</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>56570</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1151,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691964</v>
+        <v>691978</v>
       </c>
       <c r="R6" t="n">
-        <v>7128470</v>
+        <v>7128474</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121274009</v>
+        <v>121273867</v>
       </c>
       <c r="B2" t="n">
-        <v>82392</v>
+        <v>56571</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691994</v>
+        <v>691978</v>
       </c>
       <c r="R2" t="n">
-        <v>7128443</v>
+        <v>7128474</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121274056</v>
+        <v>121273967</v>
       </c>
       <c r="B3" t="n">
-        <v>5172</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692000</v>
+        <v>691964</v>
       </c>
       <c r="R3" t="n">
-        <v>7128433</v>
+        <v>7128470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -910,7 +910,7 @@
         <v>121273772</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121273967</v>
+        <v>121274056</v>
       </c>
       <c r="B5" t="n">
-        <v>78608</v>
+        <v>5172</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691964</v>
+        <v>692000</v>
       </c>
       <c r="R5" t="n">
-        <v>7128470</v>
+        <v>7128433</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121273867</v>
+        <v>121274009</v>
       </c>
       <c r="B6" t="n">
-        <v>56570</v>
+        <v>82393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,25 +1151,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691978</v>
+        <v>691994</v>
       </c>
       <c r="R6" t="n">
-        <v>7128474</v>
+        <v>7128443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121273967</v>
+        <v>121274056</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>5172</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691964</v>
+        <v>692000</v>
       </c>
       <c r="R3" t="n">
-        <v>7128470</v>
+        <v>7128433</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121274056</v>
+        <v>121274009</v>
       </c>
       <c r="B5" t="n">
-        <v>5172</v>
+        <v>82393</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692000</v>
+        <v>691994</v>
       </c>
       <c r="R5" t="n">
-        <v>7128433</v>
+        <v>7128443</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121274009</v>
+        <v>121273967</v>
       </c>
       <c r="B6" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691994</v>
+        <v>691964</v>
       </c>
       <c r="R6" t="n">
-        <v>7128443</v>
+        <v>7128470</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121273867</v>
+        <v>121273772</v>
       </c>
       <c r="B2" t="n">
-        <v>56571</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691978</v>
+        <v>691997</v>
       </c>
       <c r="R2" t="n">
-        <v>7128474</v>
+        <v>7128437</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121273772</v>
+        <v>121274009</v>
       </c>
       <c r="B4" t="n">
-        <v>90720</v>
+        <v>82393</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691997</v>
+        <v>691994</v>
       </c>
       <c r="R4" t="n">
-        <v>7128437</v>
+        <v>7128443</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121274009</v>
+        <v>121273867</v>
       </c>
       <c r="B5" t="n">
-        <v>82393</v>
+        <v>56571</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691994</v>
+        <v>691978</v>
       </c>
       <c r="R5" t="n">
-        <v>7128443</v>
+        <v>7128474</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121274056</v>
+        <v>121273867</v>
       </c>
       <c r="B3" t="n">
-        <v>5172</v>
+        <v>56571</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692000</v>
+        <v>691978</v>
       </c>
       <c r="R3" t="n">
-        <v>7128433</v>
+        <v>7128474</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121274009</v>
+        <v>121274056</v>
       </c>
       <c r="B4" t="n">
-        <v>82393</v>
+        <v>5172</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691994</v>
+        <v>692000</v>
       </c>
       <c r="R4" t="n">
-        <v>7128443</v>
+        <v>7128433</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121273867</v>
+        <v>121273967</v>
       </c>
       <c r="B5" t="n">
-        <v>56571</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691978</v>
+        <v>691964</v>
       </c>
       <c r="R5" t="n">
-        <v>7128474</v>
+        <v>7128470</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,10 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121273967</v>
+        <v>121274009</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,21 +1155,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691964</v>
+        <v>691994</v>
       </c>
       <c r="R6" t="n">
-        <v>7128470</v>
+        <v>7128443</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 59920-2021 artfynd.xlsx
+++ b/artfynd/A 59920-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121273772</v>
+        <v>121273867</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>56571</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691997</v>
+        <v>691978</v>
       </c>
       <c r="R2" t="n">
-        <v>7128437</v>
+        <v>7128474</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121273867</v>
+        <v>121273772</v>
       </c>
       <c r="B3" t="n">
-        <v>56571</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,25 +803,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691978</v>
+        <v>691997</v>
       </c>
       <c r="R3" t="n">
-        <v>7128474</v>
+        <v>7128437</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
